--- a/output/pdf_financials_xlsx/TNJ.xlsx
+++ b/output/pdf_financials_xlsx/TNJ.xlsx
@@ -724,13 +724,13 @@
         <v>-1.273571</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.487096</v>
+        <v>-1.487096</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.744463</v>
+        <v>-5.744463</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5.852312</v>
+        <v>-5.852312</v>
       </c>
     </row>
     <row r="17">
@@ -816,13 +816,13 @@
         <v>-1.273571</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.487096</v>
+        <v>-1.487096</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.744463</v>
+        <v>-5.744463</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.852312</v>
+        <v>-5.852312</v>
       </c>
     </row>
     <row r="21">
@@ -873,13 +873,13 @@
         <v>-1.273571</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.487096</v>
+        <v>-1.487096</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.744463</v>
+        <v>-5.744463</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5.852312</v>
+        <v>-5.852312</v>
       </c>
     </row>
     <row r="24">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-191.4821</v>
+        <v>191.4821</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -957,13 +957,13 @@
         <v>-1.273571</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.487096</v>
+        <v>-1.487096</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.744463</v>
+        <v>-5.744463</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.852312</v>
+        <v>-5.852312</v>
       </c>
     </row>
     <row r="28">
@@ -995,13 +995,13 @@
         <v>-1.273571</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.487096</v>
+        <v>-1.487096</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.744463</v>
+        <v>-5.744463</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.852312</v>
+        <v>-5.852312</v>
       </c>
     </row>
     <row r="30">
@@ -1041,13 +1041,13 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.271295</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.017705</v>
@@ -4626,7 +4626,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.271295</v>
       </c>
@@ -8781,7 +8785,7 @@
         </is>
       </c>
       <c r="H155" s="5" t="n">
-        <v>5.852312</v>
+        <v>-5.852312</v>
       </c>
     </row>
     <row r="156">
@@ -8859,7 +8863,7 @@
         </is>
       </c>
       <c r="H157" s="5" t="n">
-        <v>5.852312</v>
+        <v>-5.852312</v>
       </c>
     </row>
     <row r="158">
@@ -9585,10 +9589,10 @@
         </is>
       </c>
       <c r="F177" s="5" t="n">
-        <v>1.487096</v>
+        <v>-1.487096</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>5.744463</v>
+        <v>-5.744463</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TNJ.xlsx
+++ b/output/pdf_financials_xlsx/TNJ.xlsx
@@ -608,13 +608,13 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.017803</v>
+        <v>0.80392</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.111856</v>
+        <v>1.062723</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.111856</v>
+        <v>1.062723</v>
       </c>
     </row>
     <row r="11">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.017803</v>
+        <v>-0.80392</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.111856</v>
+        <v>-1.062723</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003341</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -957,7 +957,7 @@
         <v>-1.273571</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.487096</v>
+        <v>-1.490437</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.744463</v>
@@ -995,7 +995,7 @@
         <v>-1.273571</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.487096</v>
+        <v>-1.490437</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.744463</v>
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.213413</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001402</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.04064</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.134791</v>
       </c>
     </row>
     <row r="35">
@@ -1129,16 +1129,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.213413</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001402</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.04064</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.134791</v>
       </c>
     </row>
     <row r="37">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.219413</v>
+        <v>0.006</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">

--- a/output/pdf_financials_xlsx/TNJ.xlsx
+++ b/output/pdf_financials_xlsx/TNJ.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.0305</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.017803</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.0305</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.80392</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.0305</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.80392</v>
@@ -5460,7 +5460,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -9764,7 +9768,11 @@
           <t>Management and director fees 8</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="n">
         <v>0.0305</v>
       </c>
